--- a/docs/plantillas/personal_nivel_3.xlsx
+++ b/docs/plantillas/personal_nivel_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Apps\eda\docs\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83EFE528-0B1F-4AF3-AC8F-F76A9AC8684F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5994DE5F-1017-425C-9E3A-5F5CD7AE5151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F58107B5-C0CA-4530-B9BD-4A979AE2A154}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F58107B5-C0CA-4530-B9BD-4A979AE2A154}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Ranking</t>
   </si>
@@ -96,13 +94,28 @@
   </si>
   <si>
     <t>ORIENTADOR</t>
+  </si>
+  <si>
+    <t>RESERVA</t>
+  </si>
+  <si>
+    <t>Velarde</t>
+  </si>
+  <si>
+    <t>Laines</t>
+  </si>
+  <si>
+    <t>Roy</t>
+  </si>
+  <si>
+    <t>roy@hotmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,7 +176,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -183,6 +196,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -518,14 +533,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEB6D415-7385-4C92-B102-A25A2B14B0E4}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -554,11 +569,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="2" spans="1:9">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -583,7 +598,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -609,6 +624,35 @@
         <v>19</v>
       </c>
       <c r="I3" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="7">
+        <v>72586932</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="7">
+        <v>123789456</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -616,6 +660,7 @@
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" display="mailto:ana@example.com" xr:uid="{A3D024B5-37D5-4CFE-82FE-27C36EBAD768}"/>
     <hyperlink ref="F3" r:id="rId2" display="mailto:pedro@example.com" xr:uid="{D2DAF4F7-5650-44BB-8001-324E1C5FDF97}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{D3EFF169-45B2-4378-9229-A2A30471B734}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
